--- a/data/trans_orig/IQ21C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ21C-Edad-trans_orig.xlsx
@@ -2588,7 +2588,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>65,45%</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,51%</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -7152,12 +7152,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -10247,12 +10247,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10297,12 +10297,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -14453,7 +14453,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -14594,12 +14594,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -14609,12 +14609,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14710,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -17557,7 +17557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,59%</t>
         </is>
       </c>
     </row>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18097,7 +18097,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -18314,12 +18314,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18329,12 +18329,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -21632,7 +21632,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -21667,7 +21667,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -21778,7 +21778,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -21793,7 +21793,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -21819,7 +21819,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -21889,7 +21889,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -21965,7 +21965,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -22000,7 +22000,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -22056,7 +22056,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -22126,7 +22126,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22374,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -22409,7 +22409,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -22444,7 +22444,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -22485,7 +22485,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -22661,12 +22661,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -22676,12 +22676,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -30143,7 +30143,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -30158,7 +30158,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ21C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ21C-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,205 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5,0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
+        <v>0.935687003958486</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0.935687003958486</v>
+      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8,94</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,76</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,45</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,29</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5,28</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7,14</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5,49</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2,97; 10,41</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3,6; 23,07</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 6,0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 7,0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,68; 14,77</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 8,67</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3,44; 17,2</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 13,43</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.001775733183092</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>8.940232141670553</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="n">
+        <v>3.763716701682095</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>3.446508041828058</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>7.286613576540005</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.994133568450174</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5.281188253284674</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>7.14124630981506</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>5.486438014294547</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1.994133568450174</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,12</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4,05</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3,6</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,29</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2.973481842505191</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3.597880159245942</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1.678606124022831</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2.874642466552575</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>3.441439002221778</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1.247116065239074</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 6,0</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>3,0; 6,0</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 5,85</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 6,0</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10.41184644096502</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>23.07346533694899</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>14.77019804069028</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>8.67174185261346</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>17.19914207324936</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>13.42527141015624</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +857,319 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14,15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14,15</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24,0</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="n">
+        <v>3.245687142584348</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="n">
+        <v>4.11534760864848</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>4.05007760459313</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="n">
+        <v>3.599180948193037</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>3.288459807520992</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5,0; 24,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5,0; 24,0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="n">
+        <v>1.308993432695556</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="n">
+        <v>5.849769976646114</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="n">
+        <v>14.1462502083779</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="n">
+        <v>14.1462502083779</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,82</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>10,01</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,78</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,4</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,29</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3,06</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4,91</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7,13</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6,53</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3,98; 9,02</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4,57; 20,73</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 17,21</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 5,41</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 5,84</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,76; 12,67</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 6,0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3,41; 7,05</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3,69; 15,33</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3,16; 12,4</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 4,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>5.824528216749528</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>10.0117040549995</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>6.783487962433942</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.092094372359923</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3.398623865093191</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>2.495939656690903</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>6.292742909907888</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>3.059347354425384</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>4.908291560630805</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>7.128775094834062</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>6.527851752043035</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>2.663058864150678</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3.977352589402717</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>4.570030226804024</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.603195711487401</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.95490851016897</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.7618187334008142</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2.756447992739487</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>3.409575231663201</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>3.693502352574127</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>3.159197175522068</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>1.433746933250949</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>9.015038195071281</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>20.73114564541212</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>17.20635381634974</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>5.406845633220053</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>5.839270523905964</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>12.67180237597286</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>6.000000000000001</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7.047702658696782</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>15.33327834137176</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>12.39896215667485</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>4.552402015695894</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1177,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
